--- a/public/exports-60-250-with-coowners/29188505.xlsx
+++ b/public/exports-60-250-with-coowners/29188505.xlsx
@@ -1016,26 +1016,26 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halsskovvej 151</t>
+          <t xml:space="preserve">Havnevej 6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5355028</t>
+          <t xml:space="preserve">721030, 5362602</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J14">
-        <v>160</v>
+        <v>249</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1091,26 +1091,26 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halsskovvej 165</t>
+          <t xml:space="preserve">Holbækvej 16</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5353824</t>
+          <t xml:space="preserve">5369490</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J15">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1166,26 +1166,26 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnevej 6</t>
+          <t xml:space="preserve">Husmandsstræde 11</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4245</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">721030, 5362602</t>
+          <t xml:space="preserve">2515560</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J16">
-        <v>249</v>
+        <v>70</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbækvej 16</t>
+          <t xml:space="preserve">Hvilebjergvej 8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1251,16 +1251,16 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369490</t>
+          <t xml:space="preserve">720395, 2516743</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J17">
-        <v>65</v>
+        <v>189</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1316,26 +1316,26 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Husmandsstræde 11</t>
+          <t xml:space="preserve">Kirkerupvej 16A</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4245</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2515560</t>
+          <t xml:space="preserve">720398, 2516752</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J18">
-        <v>70</v>
+        <v>195</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvilebjergvej 8</t>
+          <t xml:space="preserve">Kirkerupvej 18B</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1401,16 +1401,16 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">720395, 2516743</t>
+          <t xml:space="preserve">2516403</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J19">
-        <v>189</v>
+        <v>161</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkerupvej 16A</t>
+          <t xml:space="preserve">Koldhøjvej 5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1476,16 +1476,16 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">720398, 2516752</t>
+          <t xml:space="preserve">721052, 2476238</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J20">
-        <v>195</v>
+        <v>113</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkerupvej 18B</t>
+          <t xml:space="preserve">Kongelyset 41</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2516403</t>
+          <t xml:space="preserve">721071, 5370837</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="J21">
-        <v>161</v>
+        <v>86</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Koldhøjvej 5</t>
+          <t xml:space="preserve">Langøre 1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1626,16 +1626,16 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">721052, 2476238</t>
+          <t xml:space="preserve">1320961</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J22">
-        <v>113</v>
+        <v>222</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongelyset 41</t>
+          <t xml:space="preserve">Langøre 3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1701,16 +1701,16 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">721071, 5370837</t>
+          <t xml:space="preserve">1320961</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J23">
-        <v>86</v>
+        <v>223</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1766,26 +1766,26 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langøre 1</t>
+          <t xml:space="preserve">Madevejen 51</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1320961</t>
+          <t xml:space="preserve">2515268</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J24">
-        <v>222</v>
+        <v>116</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1841,26 +1841,26 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langøre 3</t>
+          <t xml:space="preserve">Møllevangen 48</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1320961</t>
+          <t xml:space="preserve">720932, 9375989</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J25">
-        <v>223</v>
+        <v>84</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1916,26 +1916,26 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Madevejen 51</t>
+          <t xml:space="preserve">Oksebrovej 7</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2515268</t>
+          <t xml:space="preserve">721049, 9472289</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J26">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1991,26 +1991,26 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevangen 48</t>
+          <t xml:space="preserve">Oksebrovej 7</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">720932, 9375989</t>
+          <t xml:space="preserve">721049, 9472289</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J27">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2066,26 +2066,26 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oksebrovej 7</t>
+          <t xml:space="preserve">Omø Havnevej 102</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4245</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">721049, 9472289</t>
+          <t xml:space="preserve">2515638</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J28">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2141,26 +2141,26 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oksebrovej 7</t>
+          <t xml:space="preserve">Omø Havnevej 109</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4245</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">721049, 9472289</t>
+          <t xml:space="preserve">501095, 9316642</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J29">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omø Havnevej 102</t>
+          <t xml:space="preserve">Omø Havnevej 97</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2231,11 +2231,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J30">
-        <v>103</v>
+        <v>174</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omø Havnevej 109</t>
+          <t xml:space="preserve">Omø Havnevej 98</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2301,16 +2301,16 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">501095, 9316642</t>
+          <t xml:space="preserve">2515638</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J31">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2366,26 +2366,26 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omø Havnevej 97</t>
+          <t xml:space="preserve">Quistgaardsvej 6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">4245</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2515638</t>
+          <t xml:space="preserve">5355214</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J32">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2441,26 +2441,26 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omø Havnevej 98</t>
+          <t xml:space="preserve">Revvej 88</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">4245</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2515638</t>
+          <t xml:space="preserve">720582, 5354607</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J33">
-        <v>69</v>
+        <v>152</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2516,26 +2516,26 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quistgaardsvej 6</t>
+          <t xml:space="preserve">Rosenkildevej 93A</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5355214</t>
+          <t xml:space="preserve">9440066</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J34">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2591,26 +2591,26 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Revvej 88</t>
+          <t xml:space="preserve">Rytterstaldstræde 8</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">720582, 5354607</t>
+          <t xml:space="preserve">5364758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J35">
-        <v>152</v>
+        <v>82</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 93A</t>
+          <t xml:space="preserve">Rytterstaldstræde 8</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2676,16 +2676,16 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440066</t>
+          <t xml:space="preserve">5364758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J36">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2741,26 +2741,26 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rytterstaldstræde 8</t>
+          <t xml:space="preserve">Skolegade 1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5364758</t>
+          <t xml:space="preserve">5353495</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J37">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rytterstaldstræde 8</t>
+          <t xml:space="preserve">Skovly 4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2826,16 +2826,16 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5364758</t>
+          <t xml:space="preserve">721794, 100226440</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J38">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 1</t>
+          <t xml:space="preserve">Skovvej 135</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2901,16 +2901,16 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5353495</t>
+          <t xml:space="preserve">720792, 7746641</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J39">
-        <v>157</v>
+        <v>80</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovly 4</t>
+          <t xml:space="preserve">Skovvejen 83</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">721794, 100226440</t>
+          <t xml:space="preserve">721038, 9364230</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="J40">
-        <v>72</v>
+        <v>238</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 135</t>
+          <t xml:space="preserve">Solens Plads 25</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3051,16 +3051,16 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">720792, 7746641</t>
+          <t xml:space="preserve">5352695</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J41">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvejen 83</t>
+          <t xml:space="preserve">Sorøvej 73C</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">721038, 9364230</t>
+          <t xml:space="preserve">9364238</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="J42">
-        <v>238</v>
+        <v>62</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3191,17 +3191,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solens Plads 25</t>
+          <t xml:space="preserve">Spejdervænget 1</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4261</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">5352695</t>
+          <t xml:space="preserve">720394, 2512195</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3210,7 +3210,7 @@
         </is>
       </c>
       <c r="J43">
-        <v>113</v>
+        <v>187</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3266,26 +3266,26 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sorøvej 73C</t>
+          <t xml:space="preserve">Stigsnæs Landevej 600</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">9364238</t>
+          <t xml:space="preserve">2514953</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J44">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3341,17 +3341,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spejdervænget 1</t>
+          <t xml:space="preserve">Stigsnæs Landevej 602</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">4261</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">720394, 2512195</t>
+          <t xml:space="preserve">2514953</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="J45">
-        <v>187</v>
+        <v>61</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -3416,26 +3416,26 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stigsnæs Landevej 600</t>
+          <t xml:space="preserve">Strandalle 100</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4244</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2514953</t>
+          <t xml:space="preserve">2509343</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J46">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -3491,17 +3491,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stigsnæs Landevej 602</t>
+          <t xml:space="preserve">Strandalle 101</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4244</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2514953</t>
+          <t xml:space="preserve">721014, 2509345</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="J47">
-        <v>61</v>
+        <v>232</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandalle 100</t>
+          <t xml:space="preserve">Strandalle 103</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3576,16 +3576,16 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509343</t>
+          <t xml:space="preserve">720995, 2509344</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J48">
-        <v>94</v>
+        <v>185</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -3641,17 +3641,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandalle 101</t>
+          <t xml:space="preserve">Støvlebækvej 6</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">4244</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">721014, 2509345</t>
+          <t xml:space="preserve">2534510</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="J49">
-        <v>232</v>
+        <v>75</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -3716,17 +3716,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandalle 103</t>
+          <t xml:space="preserve">Svenstrup Strandvej 1A</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">4244</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">720995, 2509344</t>
+          <t xml:space="preserve">720901, 7007774</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="J50">
-        <v>185</v>
+        <v>105</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -3791,17 +3791,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Støvlebækvej 6</t>
+          <t xml:space="preserve">Teglværksvej 4</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2534510</t>
+          <t xml:space="preserve">2537303</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="J51">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svenstrup Strandvej 1A</t>
+          <t xml:space="preserve">Tovesvej 30C</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3876,16 +3876,16 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">720901, 7007774</t>
+          <t xml:space="preserve">5357820</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J52">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3941,17 +3941,17 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teglværksvej 4</t>
+          <t xml:space="preserve">Trestensvej 1A</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2537303</t>
+          <t xml:space="preserve">720984, 2509857</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3960,7 +3960,7 @@
         </is>
       </c>
       <c r="J53">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4016,26 +4016,26 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tovesvej 30C</t>
+          <t xml:space="preserve">Trestensvej 3A</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5357820</t>
+          <t xml:space="preserve">2509859</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J54">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4091,17 +4091,17 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trestensvej 1A</t>
+          <t xml:space="preserve">Ørnumvej 25</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">720984, 2509857</t>
+          <t xml:space="preserve">720777, 8137575</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="J55">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4166,26 +4166,26 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trestensvej 3A</t>
+          <t xml:space="preserve">Ørnumvej 8</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509859</t>
+          <t xml:space="preserve">720933, 10220761</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J56">
-        <v>185</v>
+        <v>129</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørnumvej 25</t>
+          <t xml:space="preserve">Ørnumvej 8A</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4251,16 +4251,16 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">720777, 8137575</t>
+          <t xml:space="preserve">10220761</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J57">
-        <v>142</v>
+        <v>90</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4316,30 +4316,30 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørnumvej 8</t>
+          <t xml:space="preserve">Gamlevej 2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4244</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">720933, 10220761</t>
+          <t xml:space="preserve">2509084</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J58">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200025762</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4349,12 +4349,12 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-12-17</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -4391,45 +4391,45 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørnumvej 8A</t>
+          <t xml:space="preserve">Havnevej 14</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">10220761</t>
+          <t xml:space="preserve">720998, 5362593</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J59">
-        <v>90</v>
+        <v>155</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200025891</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S (Slagelse)</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-12-19</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -4466,40 +4466,40 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gamlevej 2</t>
+          <t xml:space="preserve">Havnevej 22</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">4244</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509084</t>
+          <t xml:space="preserve">5362593</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J60">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025762</t>
+          <t xml:space="preserve">200025891</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S (Slagelse)</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-17</t>
+          <t xml:space="preserve">2019-12-19</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4541,40 +4541,40 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnevej 14</t>
+          <t xml:space="preserve">Møllevangen 29</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">720998, 5362593</t>
+          <t xml:space="preserve">720568, 5357290</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J61">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025891</t>
+          <t xml:space="preserve">200028016</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S (Slagelse)</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-19</t>
+          <t xml:space="preserve">2020-02-12</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4616,22 +4616,22 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnevej 22</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4241</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5362593</t>
+          <t xml:space="preserve">2539618</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J62">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025891</t>
+          <t xml:space="preserve">200031143</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-19</t>
+          <t xml:space="preserve">2020-05-05</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4691,40 +4691,40 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevangen 29</t>
+          <t xml:space="preserve">Rosenkildevej 93</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">720568, 5357290</t>
+          <t xml:space="preserve">9440066</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J63">
-        <v>120</v>
+        <v>248</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">200028016</t>
+          <t xml:space="preserve">200050216</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S (Slagelse)</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-12</t>
+          <t xml:space="preserve">2021-06-14</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4766,50 +4766,50 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Skolevej 8</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">4241</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2539618</t>
+          <t xml:space="preserve">2509761</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J64">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">200031143</t>
+          <t xml:space="preserve">311292459</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S (Slagelse)</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-05-05</t>
+          <t xml:space="preserve">2028-01-12</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 93</t>
+          <t xml:space="preserve">Rosenkildevej 101A</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4851,40 +4851,40 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440066</t>
+          <t xml:space="preserve">5369974</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J65">
-        <v>248</v>
+        <v>167</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">200050216</t>
+          <t xml:space="preserve">311313184</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S (Slagelse)</t>
+          <t xml:space="preserve">TRANEKAER-ARKITEKTKONTOR.DK aps</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-06-14</t>
+          <t xml:space="preserve">2028-05-09</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4916,17 +4916,17 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 8</t>
+          <t xml:space="preserve">Holbækvej 16</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509761</t>
+          <t xml:space="preserve">5369490</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4935,21 +4935,21 @@
         </is>
       </c>
       <c r="J66">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311292459</t>
+          <t xml:space="preserve">311315035</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">ARKIdesign ApS</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-12</t>
+          <t xml:space="preserve">2028-05-18</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4991,40 +4991,40 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 101A</t>
+          <t xml:space="preserve">Tjærebyvej 3</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369974</t>
+          <t xml:space="preserve">2538110</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J67">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311313184</t>
+          <t xml:space="preserve">311356846</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRANEKAER-ARKITEKTKONTOR.DK aps</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-09</t>
+          <t xml:space="preserve">2029-01-28</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5066,40 +5066,40 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbækvej 16</t>
+          <t xml:space="preserve">Tjærebyvej 5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369490</t>
+          <t xml:space="preserve">2538110</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J68">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311315035</t>
+          <t xml:space="preserve">311356857</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARKIdesign ApS</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-18</t>
+          <t xml:space="preserve">2029-01-28</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5141,40 +5141,40 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjærebyvej 3</t>
+          <t xml:space="preserve">Blomstervænget 4</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4261</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2538110</t>
+          <t xml:space="preserve">2512265</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J69">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311356846</t>
+          <t xml:space="preserve">311459672</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-28</t>
+          <t xml:space="preserve">2030-09-08</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5216,40 +5216,40 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjærebyvej 5</t>
+          <t xml:space="preserve">Bildsøvej 80A</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2538110</t>
+          <t xml:space="preserve">2534051</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J70">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311356857</t>
+          <t xml:space="preserve">311463723</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-28</t>
+          <t xml:space="preserve">2030-09-28</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5291,17 +5291,17 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blomstervænget 4</t>
+          <t xml:space="preserve">Næstved Landevej 628</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">4261</t>
+          <t xml:space="preserve">4243</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2512265</t>
+          <t xml:space="preserve">2517720</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5310,11 +5310,11 @@
         </is>
       </c>
       <c r="J71">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311459672</t>
+          <t xml:space="preserve">311491481</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-08</t>
+          <t xml:space="preserve">2031-01-29</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5366,30 +5366,30 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bildsøvej 80A</t>
+          <t xml:space="preserve">Næstved Landevej 632A</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4243</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2534051</t>
+          <t xml:space="preserve">9316694</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J72">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311463723</t>
+          <t xml:space="preserve">311493572</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-28</t>
+          <t xml:space="preserve">2031-02-08</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5441,17 +5441,17 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næstved Landevej 628</t>
+          <t xml:space="preserve">Søbatteriet 5</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">4243</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2517720</t>
+          <t xml:space="preserve">9065073</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5460,21 +5460,21 @@
         </is>
       </c>
       <c r="J73">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311491481</t>
+          <t xml:space="preserve">311521545</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-29</t>
+          <t xml:space="preserve">2031-05-20</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5516,30 +5516,30 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næstved Landevej 632A</t>
+          <t xml:space="preserve">Rosenkildevej 92</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">4243</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">9316694</t>
+          <t xml:space="preserve">5367460</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J74">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311493572</t>
+          <t xml:space="preserve">311525848</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-08</t>
+          <t xml:space="preserve">2031-06-07</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5591,17 +5591,17 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søbatteriet 5</t>
+          <t xml:space="preserve">Industrivej 9</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">9065073</t>
+          <t xml:space="preserve">5369721</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5610,21 +5610,21 @@
         </is>
       </c>
       <c r="J75">
-        <v>63</v>
+        <v>139</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311521545</t>
+          <t xml:space="preserve">311531549</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-20</t>
+          <t xml:space="preserve">2031-06-28</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 92</t>
+          <t xml:space="preserve">Industrivej 9A</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5676,20 +5676,20 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5367460</t>
+          <t xml:space="preserve">5369721</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J76">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311525853</t>
+          <t xml:space="preserve">311531554</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-07</t>
+          <t xml:space="preserve">2031-06-28</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5741,30 +5741,30 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 9</t>
+          <t xml:space="preserve">Skolevej 8</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369721</t>
+          <t xml:space="preserve">2509761</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J77">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311531549</t>
+          <t xml:space="preserve">311539890</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-28</t>
+          <t xml:space="preserve">2031-08-10</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5816,30 +5816,30 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 9A</t>
+          <t xml:space="preserve">Skolevej 8</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369721</t>
+          <t xml:space="preserve">2509761</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J78">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311531554</t>
+          <t xml:space="preserve">311545732</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-28</t>
+          <t xml:space="preserve">2031-09-03</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5906,15 +5906,15 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J79">
-        <v>118</v>
+        <v>179</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539890</t>
+          <t xml:space="preserve">311546553</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-10</t>
+          <t xml:space="preserve">2031-09-08</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -5981,15 +5981,15 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J80">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311545732</t>
+          <t xml:space="preserve">311546650</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-03</t>
+          <t xml:space="preserve">2031-09-08</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6056,15 +6056,15 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J81">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311546553</t>
+          <t xml:space="preserve">311546894</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-08</t>
+          <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J82">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311546650</t>
+          <t xml:space="preserve">311546893</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-08</t>
+          <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 8</t>
+          <t xml:space="preserve">Skolevej 6</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6206,15 +6206,15 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J83">
-        <v>158</v>
+        <v>236</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311546894</t>
+          <t xml:space="preserve">311547259</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-09</t>
+          <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6281,15 +6281,15 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J84">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311546893</t>
+          <t xml:space="preserve">311547262</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-09</t>
+          <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 6</t>
+          <t xml:space="preserve">Møllebakken 3A</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6351,20 +6351,20 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509761</t>
+          <t xml:space="preserve">5363800</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J85">
-        <v>236</v>
+        <v>137</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547259</t>
+          <t xml:space="preserve">311547930</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-10</t>
+          <t xml:space="preserve">2031-09-14</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 8</t>
+          <t xml:space="preserve">Møllebakken 3B</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6426,20 +6426,20 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509761</t>
+          <t xml:space="preserve">5363800</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J86">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547262</t>
+          <t xml:space="preserve">311547944</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-10</t>
+          <t xml:space="preserve">2031-09-14</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6491,30 +6491,30 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllebakken 3A</t>
+          <t xml:space="preserve">Gormsvej 20</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">5363800</t>
+          <t xml:space="preserve">5373175</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J87">
-        <v>137</v>
+        <v>223</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547930</t>
+          <t xml:space="preserve">311548621</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-14</t>
+          <t xml:space="preserve">2031-09-16</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6566,30 +6566,30 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllebakken 3B</t>
+          <t xml:space="preserve">Tovesvej 30E</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">5363800</t>
+          <t xml:space="preserve">720845, 5357819</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J88">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547944</t>
+          <t xml:space="preserve">311549281</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-14</t>
+          <t xml:space="preserve">2031-09-20</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6641,17 +6641,17 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gormsvej 20</t>
+          <t xml:space="preserve">Borgbjergvej 7A</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4242</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">5373175</t>
+          <t xml:space="preserve">2529968</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6660,11 +6660,11 @@
         </is>
       </c>
       <c r="J89">
-        <v>223</v>
+        <v>120</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548621</t>
+          <t xml:space="preserve">311550961</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-16</t>
+          <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6716,30 +6716,30 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tovesvej 30E</t>
+          <t xml:space="preserve">Borgbjergvej 7C</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4242</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">720845, 5357819</t>
+          <t xml:space="preserve">2529968</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J90">
-        <v>141</v>
+        <v>240</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549281</t>
+          <t xml:space="preserve">311550961</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-20</t>
+          <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6791,30 +6791,30 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tovesvej 66</t>
+          <t xml:space="preserve">Borgbjergvej 7G</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4242</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">5357818</t>
+          <t xml:space="preserve">2529968</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J91">
-        <v>134</v>
+        <v>191</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549269</t>
+          <t xml:space="preserve">311550961</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-20</t>
+          <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgbjergvej 7A</t>
+          <t xml:space="preserve">Borgbjergvej 7M</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J92">
@@ -6941,30 +6941,30 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgbjergvej 7C</t>
+          <t xml:space="preserve">Halsebyvænget 14</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">4242</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2529968</t>
+          <t xml:space="preserve">100051113</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J93">
-        <v>240</v>
+        <v>116</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311550961</t>
+          <t xml:space="preserve">311560288</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-27</t>
+          <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7016,30 +7016,30 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgbjergvej 7G</t>
+          <t xml:space="preserve">Halsebyvænget 18</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">4242</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2529968</t>
+          <t xml:space="preserve">100051113</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J94">
-        <v>191</v>
+        <v>116</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311550961</t>
+          <t xml:space="preserve">311560278</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-27</t>
+          <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7091,30 +7091,30 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgbjergvej 7M</t>
+          <t xml:space="preserve">Halsebyvænget 2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">4242</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2529968</t>
+          <t xml:space="preserve">100051113</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J95">
-        <v>120</v>
+        <v>177</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311550961</t>
+          <t xml:space="preserve">311560285</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-27</t>
+          <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halsebyvænget 14</t>
+          <t xml:space="preserve">Halsebyvænget 22</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J96">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560288</t>
+          <t xml:space="preserve">311560286</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halsebyvænget 18</t>
+          <t xml:space="preserve">Halsebyvænget 26</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7256,15 +7256,15 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J97">
-        <v>116</v>
+        <v>220</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560278</t>
+          <t xml:space="preserve">311560221</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halsebyvænget 2</t>
+          <t xml:space="preserve">Halsebyvænget 52</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -7331,15 +7331,15 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J98">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560285</t>
+          <t xml:space="preserve">311560219</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halsebyvænget 22</t>
+          <t xml:space="preserve">Halsebyvænget 8</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7406,15 +7406,15 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J99">
-        <v>116</v>
+        <v>177</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560286</t>
+          <t xml:space="preserve">311560289</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7466,30 +7466,30 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halsebyvænget 26</t>
+          <t xml:space="preserve">Vejsgård Alle 1</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4241</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">100051113</t>
+          <t xml:space="preserve">100051431</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J100">
-        <v>220</v>
+        <v>132</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560221</t>
+          <t xml:space="preserve">311561813</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-08</t>
+          <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7541,30 +7541,30 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halsebyvænget 52</t>
+          <t xml:space="preserve">Vejsgård Alle 12</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4241</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">100051113</t>
+          <t xml:space="preserve">100051431</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J101">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560219</t>
+          <t xml:space="preserve">311561833</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-08</t>
+          <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7616,30 +7616,30 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halsebyvænget 8</t>
+          <t xml:space="preserve">Vejsgård Alle 16</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4241</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">100051113</t>
+          <t xml:space="preserve">100051431</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J102">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560289</t>
+          <t xml:space="preserve">311561855</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-08</t>
+          <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejsgård Alle 1</t>
+          <t xml:space="preserve">Vejsgård Alle 2</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7706,15 +7706,15 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J103">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561813</t>
+          <t xml:space="preserve">311561831</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejsgård Alle 12</t>
+          <t xml:space="preserve">Vejsgård Alle 22</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7781,15 +7781,15 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J104">
-        <v>113</v>
+        <v>184</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561833</t>
+          <t xml:space="preserve">311561858</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejsgård Alle 16</t>
+          <t xml:space="preserve">Vejsgård Alle 28</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7856,15 +7856,15 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J105">
-        <v>173</v>
+        <v>113</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561855</t>
+          <t xml:space="preserve">311561820</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejsgård Alle 2</t>
+          <t xml:space="preserve">Vejsgård Alle 3</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7931,15 +7931,15 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J106">
-        <v>113</v>
+        <v>187</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561831</t>
+          <t xml:space="preserve">311561805</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejsgård Alle 22</t>
+          <t xml:space="preserve">Vejsgård Alle 32</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J107">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561858</t>
+          <t xml:space="preserve">311561818</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejsgård Alle 28</t>
+          <t xml:space="preserve">Vejsgård Alle 38</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J108">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561820</t>
+          <t xml:space="preserve">311561815</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejsgård Alle 3</t>
+          <t xml:space="preserve">Vejsgård Alle 5</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J109">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561805</t>
+          <t xml:space="preserve">311561809</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejsgård Alle 32</t>
+          <t xml:space="preserve">Vejsgård Alle 6</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8231,15 +8231,15 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J110">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561818</t>
+          <t xml:space="preserve">311561837</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8291,30 +8291,30 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejsgård Alle 38</t>
+          <t xml:space="preserve">Park Alle 68</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">4241</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">100051431</t>
+          <t xml:space="preserve">100048065</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J111">
-        <v>113</v>
+        <v>227</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561815</t>
+          <t xml:space="preserve">311562133</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-15</t>
+          <t xml:space="preserve">2031-11-16</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8366,17 +8366,17 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejsgård Alle 5</t>
+          <t xml:space="preserve">Slagelse Landevej 3</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">4241</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">100051431</t>
+          <t xml:space="preserve">9449078</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -8385,11 +8385,11 @@
         </is>
       </c>
       <c r="J112">
-        <v>187</v>
+        <v>87</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561809</t>
+          <t xml:space="preserve">311563195</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-15</t>
+          <t xml:space="preserve">2031-11-22</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8441,17 +8441,17 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejsgård Alle 6</t>
+          <t xml:space="preserve">Nygade 47</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">4241</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">100051431</t>
+          <t xml:space="preserve">5352531</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -8460,11 +8460,11 @@
         </is>
       </c>
       <c r="J113">
-        <v>173</v>
+        <v>120</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561837</t>
+          <t xml:space="preserve">311566473</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-15</t>
+          <t xml:space="preserve">2031-12-07</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8516,17 +8516,17 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Park Alle 68</t>
+          <t xml:space="preserve">Holmstrupvej 5</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">100048065</t>
+          <t xml:space="preserve">5372195</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -8535,11 +8535,11 @@
         </is>
       </c>
       <c r="J114">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562133</t>
+          <t xml:space="preserve">311569055</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-16</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8591,30 +8591,30 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slagelse Landevej 3</t>
+          <t xml:space="preserve">Holmstrupvej 5</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">9449078</t>
+          <t xml:space="preserve">5372195</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J115">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311563195</t>
+          <t xml:space="preserve">311569066</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-22</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8666,30 +8666,30 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 47</t>
+          <t xml:space="preserve">Brovej 1</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">5352531</t>
+          <t xml:space="preserve">2532379</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J116">
-        <v>120</v>
+        <v>209</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566473</t>
+          <t xml:space="preserve">311569779</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-07</t>
+          <t xml:space="preserve">2031-12-23</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmstrupvej 5</t>
+          <t xml:space="preserve">Holbækvej 16</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372195</t>
+          <t xml:space="preserve">5369490</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -8760,11 +8760,11 @@
         </is>
       </c>
       <c r="J117">
-        <v>203</v>
+        <v>135</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569055</t>
+          <t xml:space="preserve">311569796</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2031-12-23</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8816,30 +8816,30 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmstrupvej 5</t>
+          <t xml:space="preserve">Norvænget 32</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372195</t>
+          <t xml:space="preserve">2510279</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J118">
-        <v>125</v>
+        <v>223</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569066</t>
+          <t xml:space="preserve">311570885</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2032-01-06</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8891,30 +8891,30 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brovej 1</t>
+          <t xml:space="preserve">Norvænget 38</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2532379</t>
+          <t xml:space="preserve">2510279</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J119">
-        <v>209</v>
+        <v>146</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569779</t>
+          <t xml:space="preserve">311570953</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-23</t>
+          <t xml:space="preserve">2032-01-06</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8966,30 +8966,30 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbækvej 16</t>
+          <t xml:space="preserve">Norvænget 12</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369490</t>
+          <t xml:space="preserve">2510279</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J120">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569796</t>
+          <t xml:space="preserve">311571124</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-23</t>
+          <t xml:space="preserve">2032-01-07</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norvænget 32</t>
+          <t xml:space="preserve">Norvænget 16</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J121">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570885</t>
+          <t xml:space="preserve">311571126</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-06</t>
+          <t xml:space="preserve">2032-01-07</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norvænget 38</t>
+          <t xml:space="preserve">Norvænget 2</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -9131,15 +9131,15 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J122">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570953</t>
+          <t xml:space="preserve">311571117</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-06</t>
+          <t xml:space="preserve">2032-01-07</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9191,30 +9191,30 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norvænget 12</t>
+          <t xml:space="preserve">Drøsselbjergvej 40A</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2510279</t>
+          <t xml:space="preserve">1321129</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J123">
-        <v>150</v>
+        <v>241</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571124</t>
+          <t xml:space="preserve">311571899</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-07</t>
+          <t xml:space="preserve">2032-01-12</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9266,30 +9266,30 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norvænget 16</t>
+          <t xml:space="preserve">Husmandsstræde 4A</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4245</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2510279</t>
+          <t xml:space="preserve">2515317</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J124">
-        <v>223</v>
+        <v>104</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571126</t>
+          <t xml:space="preserve">311571924</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-07</t>
+          <t xml:space="preserve">2032-01-12</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9341,30 +9341,30 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norvænget 2</t>
+          <t xml:space="preserve">Drøsselbjergvej 42A</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2510279</t>
+          <t xml:space="preserve">1321129</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J125">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571117</t>
+          <t xml:space="preserve">311573835</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-07</t>
+          <t xml:space="preserve">2032-01-21</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9416,30 +9416,30 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drøsselbjergvej 40A</t>
+          <t xml:space="preserve">Tjærebyvej 13</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1321129</t>
+          <t xml:space="preserve">2538110</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J126">
-        <v>241</v>
+        <v>113</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571899</t>
+          <t xml:space="preserve">311577779</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-12</t>
+          <t xml:space="preserve">2032-02-09</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9491,30 +9491,30 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Husmandsstræde 4A</t>
+          <t xml:space="preserve">Tjærebyvej 7</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">4245</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2515317</t>
+          <t xml:space="preserve">2538110</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J127">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571924</t>
+          <t xml:space="preserve">311577742</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-12</t>
+          <t xml:space="preserve">2032-02-09</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drøsselbjergvej 42A</t>
+          <t xml:space="preserve">Byskov Alle 41</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -9576,20 +9576,20 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1321129</t>
+          <t xml:space="preserve">5369956</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J128">
-        <v>100</v>
+        <v>220</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311573835</t>
+          <t xml:space="preserve">311579646</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-21</t>
+          <t xml:space="preserve">2032-02-18</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9641,40 +9641,40 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjærebyvej 13</t>
+          <t xml:space="preserve">Århusvej 2C</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2538110</t>
+          <t xml:space="preserve">273800</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J129">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311577779</t>
+          <t xml:space="preserve">311728948</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-09</t>
+          <t xml:space="preserve">2033-12-13</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9716,40 +9716,40 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjærebyvej 7</t>
+          <t xml:space="preserve">Flakkebjerg Hovedgade 40</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2538110</t>
+          <t xml:space="preserve">8007086</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J130">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311577742</t>
+          <t xml:space="preserve">311833542</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-09</t>
+          <t xml:space="preserve">2035-05-22</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byskov Alle 41</t>
+          <t xml:space="preserve">Sverigesvej 18</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9801,20 +9801,20 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369956</t>
+          <t xml:space="preserve">5370586</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J131">
-        <v>220</v>
+        <v>125</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311579646</t>
+          <t xml:space="preserve">311842904</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-18</t>
+          <t xml:space="preserve">2035-07-04</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9866,30 +9866,30 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Århusvej 2C</t>
+          <t xml:space="preserve">Næstved Landevej 630</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4243</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">273800</t>
+          <t xml:space="preserve">2517719</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J132">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728948</t>
+          <t xml:space="preserve">311843201</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-13</t>
+          <t xml:space="preserve">2035-07-07</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flakkebjerg Hovedgade 40</t>
+          <t xml:space="preserve">Byskovvej 2</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9951,30 +9951,30 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">8007086</t>
+          <t xml:space="preserve">5370601</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J133">
-        <v>152</v>
+        <v>210</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311833542</t>
+          <t xml:space="preserve">311843901</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-22</t>
+          <t xml:space="preserve">2035-07-09</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sverigesvej 18</t>
+          <t xml:space="preserve">Æblehaven 1</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -10026,20 +10026,20 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5370586</t>
+          <t xml:space="preserve">9440066</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J134">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842904</t>
+          <t xml:space="preserve">311850202</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-04</t>
+          <t xml:space="preserve">2035-08-20</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10091,40 +10091,40 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næstved Landevej 630</t>
+          <t xml:space="preserve">Æblehaven 3</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">4243</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2517719</t>
+          <t xml:space="preserve">9440066</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J135">
-        <v>101</v>
+        <v>160</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843201</t>
+          <t xml:space="preserve">311850223</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-07</t>
+          <t xml:space="preserve">2035-08-20</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10166,17 +10166,17 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byskovvej 2</t>
+          <t xml:space="preserve">Tovesvej 30A</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5370601</t>
+          <t xml:space="preserve">5357818</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -10185,11 +10185,11 @@
         </is>
       </c>
       <c r="J136">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843901</t>
+          <t xml:space="preserve">311854045</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-09</t>
+          <t xml:space="preserve">2035-09-05</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Æblehaven 1</t>
+          <t xml:space="preserve">Rosenkildevej 103</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -10251,20 +10251,20 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440066</t>
+          <t xml:space="preserve">5369970</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J137">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850202</t>
+          <t xml:space="preserve">311865637</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-20</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Æblehaven 3</t>
+          <t xml:space="preserve">Smedegade 36</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -10326,30 +10326,30 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440066</t>
+          <t xml:space="preserve">5369006</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J138">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850223</t>
+          <t xml:space="preserve">311865677</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-20</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10391,40 +10391,40 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tovesvej 30A</t>
+          <t xml:space="preserve">Æblehaven 5</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">5357818</t>
+          <t xml:space="preserve">9440066</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J139">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311854045</t>
+          <t xml:space="preserve">311865671</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-05</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 103</t>
+          <t xml:space="preserve">Rosenkildevej 88A</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10476,20 +10476,20 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369970</t>
+          <t xml:space="preserve">7711432</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J140">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865637</t>
+          <t xml:space="preserve">311866569</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-31</t>
+          <t xml:space="preserve">2035-11-05</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedegade 36</t>
+          <t xml:space="preserve">Krænkerupvej 54</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -10551,30 +10551,30 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369006</t>
+          <t xml:space="preserve">2476133</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J141">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865677</t>
+          <t xml:space="preserve">311868284</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-31</t>
+          <t xml:space="preserve">2035-11-14</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10616,40 +10616,40 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Æblehaven 5</t>
+          <t xml:space="preserve">Dyrehovedgårds Alle 24</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440066</t>
+          <t xml:space="preserve">10220761</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J142">
-        <v>184</v>
+        <v>93</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865671</t>
+          <t xml:space="preserve">311870709</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-31</t>
+          <t xml:space="preserve">2035-11-28</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10691,30 +10691,30 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 88A</t>
+          <t xml:space="preserve">Havnevej 20</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">7711432</t>
+          <t xml:space="preserve">5362593</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J143">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866569</t>
+          <t xml:space="preserve">311871351</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-05</t>
+          <t xml:space="preserve">2035-12-02</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,30 +10766,30 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krænkerupvej 54</t>
+          <t xml:space="preserve">Kruusesmindevej 3D</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2476133</t>
+          <t xml:space="preserve">9813012</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J144">
-        <v>181</v>
+        <v>212</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868284</t>
+          <t xml:space="preserve">311876540</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-14</t>
+          <t xml:space="preserve">2036-01-14</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyrehovedgårds Alle 24</t>
+          <t xml:space="preserve">Kruusesmindevej 3E</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -10851,20 +10851,20 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">10220761</t>
+          <t xml:space="preserve">9813012</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J145">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311870709</t>
+          <t xml:space="preserve">311876511</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-28</t>
+          <t xml:space="preserve">2036-01-14</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10916,30 +10916,30 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnevej 20</t>
+          <t xml:space="preserve">Tjærebyvej 11</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5362593</t>
+          <t xml:space="preserve">8085466</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J146">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871351</t>
+          <t xml:space="preserve">311913527</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-02</t>
+          <t xml:space="preserve">2036-07-08</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10991,30 +10991,30 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kruusesmindevej 3D</t>
+          <t xml:space="preserve">Rosenkildevej 81A</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">9813012</t>
+          <t xml:space="preserve">9440066</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="J147">
-        <v>212</v>
+        <v>111</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876540</t>
+          <t xml:space="preserve">311927530</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-14</t>
+          <t xml:space="preserve">2036-09-23</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11066,30 +11066,30 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kruusesmindevej 3E</t>
+          <t xml:space="preserve">Rosenkildevej 81B</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">9813012</t>
+          <t xml:space="preserve">9440066</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="J148">
-        <v>71</v>
+        <v>131</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876511</t>
+          <t xml:space="preserve">311927526</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-14</t>
+          <t xml:space="preserve">2036-09-23</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11141,30 +11141,30 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjærebyvej 11</t>
+          <t xml:space="preserve">Blomstervænget 5</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4261</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">8085466</t>
+          <t xml:space="preserve">7000144</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J149">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311913527</t>
+          <t xml:space="preserve">311928778</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-08</t>
+          <t xml:space="preserve">2036-09-29</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11216,30 +11216,30 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 81A</t>
+          <t xml:space="preserve">Halsskovvej 151</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440066</t>
+          <t xml:space="preserve">5355028</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J150">
-        <v>111</v>
+        <v>160</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311927530</t>
+          <t xml:space="preserve">311929459</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-23</t>
+          <t xml:space="preserve">2036-10-01</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11291,30 +11291,30 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 81B</t>
+          <t xml:space="preserve">Revvej 126</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440066</t>
+          <t xml:space="preserve">9375962</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J151">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311927526</t>
+          <t xml:space="preserve">311929317</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-23</t>
+          <t xml:space="preserve">2036-10-01</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11366,22 +11366,22 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blomstervænget 5</t>
+          <t xml:space="preserve">Tovesvej 66</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">4261</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000144</t>
+          <t xml:space="preserve">5357818</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J152">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311928778</t>
+          <t xml:space="preserve">311929335</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-29</t>
+          <t xml:space="preserve">2036-10-01</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Revvej 126</t>
+          <t xml:space="preserve">Halsskovvej 165</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -11451,20 +11451,20 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">9375962</t>
+          <t xml:space="preserve">5353824</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J153">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929317</t>
+          <t xml:space="preserve">311929815</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11474,7 +11474,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-10-01</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
